--- a/attachments/DSJ_AE_AI_and_DataBusiness_Analytics_Methodologies_and_Applications.xlsx
+++ b/attachments/DSJ_AE_AI_and_DataBusiness_Analytics_Methodologies_and_Applications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAABCD4-0ABC-4C5E-BE0F-20065CD2AAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D968D94F-2F73-4886-A655-87C958C4C165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="168">
   <si>
     <t>First Name</t>
   </si>
@@ -522,13 +522,28 @@
   </si>
   <si>
     <t>Product Innovation</t>
+  </si>
+  <si>
+    <t>Zhichao</t>
+  </si>
+  <si>
+    <t>Feng</t>
+  </si>
+  <si>
+    <t>zhi-chao.feng@polyu.edu.hk</t>
+  </si>
+  <si>
+    <t>Department of Logistics and Maritime Studies</t>
+  </si>
+  <si>
+    <t>The Hong Kong Polytechnic University</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -547,6 +562,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -607,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -621,11 +642,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -858,726 +880,745 @@
     <col min="9" max="12" width="46.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-    </row>
-    <row r="3" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="9" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="11" t="s">
+    <row r="15" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="K21" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="7" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" spans="1:12" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="23" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="24" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="25" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" s="1"/>
@@ -1635,9 +1676,9 @@
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="J33" s="7"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1659,8 +1700,8 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="8"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="11"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -2619,7 +2660,7 @@
   <customSheetViews>
     <customSheetView guid="{7E9A717F-8565-4B7E-B2E7-96165FD3A5DC}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:L46" xr:uid="{660548C0-0B88-4E50-B75C-D73C678AF6CF}"/>
+      <autoFilter ref="A1:L46" xr:uid="{538307CD-5AAC-4443-857A-2394AF3DA4CD}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1469349972"/>
